--- a/ai_logs/NguyenTruongPhuc_AI_Log.xlsx
+++ b/ai_logs/NguyenTruongPhuc_AI_Log.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="265">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -800,6 +800,24 @@
   </si>
   <si>
     <t>Corrected the relationships and updated the final UML diagram.</t>
+  </si>
+  <si>
+    <t>H002</t>
+  </si>
+  <si>
+    <t>Incorrect MVC Classification</t>
+  </si>
+  <si>
+    <t>AI classified some classes as MVC components.</t>
+  </si>
+  <si>
+    <t>A few classes were placed in inappropriate layers and did not strictly follow the project architecture.</t>
+  </si>
+  <si>
+    <t>Compared the generated design with the MVC structure required by the project specification.</t>
+  </si>
+  <si>
+    <t>Reorganized the classes into Model, View, Controller, and Repository layers before final submission.</t>
   </si>
 </sst>
 </file>
@@ -1967,15 +1985,25 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+        <v>259</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>

--- a/ai_logs/NguyenTruongPhuc_AI_Log.xlsx
+++ b/ai_logs/NguyenTruongPhuc_AI_Log.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="287">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -730,60 +730,6 @@
     <t>QE180176</t>
   </si>
   <si>
-    <t>Class Diagram Design</t>
-  </si>
-  <si>
-    <t>Identify core classes for the HR &amp; Payroll System</t>
-  </si>
-  <si>
-    <t>Generate UML classes for an HR Management and Payroll System</t>
-  </si>
-  <si>
-    <t>AI suggested Employee, Department, LeaveRequest, LeaveBalance, AttendanceRecord, PayrollEntry, and related classes.</t>
-  </si>
-  <si>
-    <t>Selected only the classes required by the project and removed unnecessary suggestions.</t>
-  </si>
-  <si>
-    <t>Class Diagram v1 screenshot</t>
-  </si>
-  <si>
-    <t>UML Modeling</t>
-  </si>
-  <si>
-    <t>Define relationships and create UML diagrams</t>
-  </si>
-  <si>
-    <t>Suggest relationships, multiplicities, and convert UML to Mermaid/PlantUML.</t>
-  </si>
-  <si>
-    <t>AI generated class relationships and UML code.</t>
-  </si>
-  <si>
-    <t>Adjusted multiplicities and added missing dependencies based on project requirements.</t>
-  </si>
-  <si>
-    <t>Mermaid code, PlantUML code, GitHub diagram screenshot</t>
-  </si>
-  <si>
-    <t>MVC Architecture Review</t>
-  </si>
-  <si>
-    <t>Verify MVC compliance</t>
-  </si>
-  <si>
-    <t>Review the UML diagram and validate MVC architecture.</t>
-  </si>
-  <si>
-    <t>AI identified Model, View, Controller and Repository components.</t>
-  </si>
-  <si>
-    <t>Confirmed MVC structure and refined final diagram organization.</t>
-  </si>
-  <si>
-    <t>Final UML diagram screenshot</t>
-  </si>
-  <si>
     <t>H001</t>
   </si>
   <si>
@@ -818,6 +764,126 @@
   </si>
   <si>
     <t>Reorganized the classes into Model, View, Controller, and Repository layers before final submission.</t>
+  </si>
+  <si>
+    <t>hãy đọc file Bản sao của LAB211_Payroll_De_Tai và hảy thiết kế cho tôi phần Thiết kế Class Diagram đầy đủ. Thiết kế schema 7 file CSV (cột, kiểu dữ liệu, quan hệ FK).</t>
+  </si>
+  <si>
+    <t>Thiết kế Class Diagram và cấu trúc phẳng gồm 7 file CSV để lưu trữ dữ liệu thô không dùng SQL Database.</t>
+  </si>
+  <si>
+    <t>AI đề xuất cấu trúc 7 file chi tiết nhưng cố tình nhét thêm các bảng trung gian phức tạp để lưu lịch sử biến động.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Gợi ý của AI làm tăng độ phức tạp không cần thiết cho việc xử lý File I/O tuần tự. \nContextualization: Dự án Tuần 1-2 chỉ cần ưu tiên cấu trúc phẳng tối giản. \nCreative Synthesis: Tôi quyết định bóc tách dữ liệu, gộp mã quy tắc lương trực tiếp vào thực thể Employee. \nDecision: Giữ lại DataGenerator và 7 file CSV cấu trúc đơn giản để khớp tiến độ.</t>
+  </si>
+  <si>
+    <t>Thư mục data/ chứa 7 tệp CSV.</t>
+  </si>
+  <si>
+    <t>Tạo tệp mã nguồn DataGenerator.java để sinh tự động khối lượng dữ liệu lớn nhằm mục đích chạy kiểm thử.</t>
+  </si>
+  <si>
+    <t>Viết class DataGenerator bằng Java để ghi ngẫu nhiên dữ liệu vòng lặp đạt &gt;=10,000 dòng vào các file CSV tương ứng và attendance.csv &gt;=12,000 dòng.</t>
+  </si>
+  <si>
+    <t>AI cung cấp vòng lặp sử dụng hàm ngẫu nhiên Math.random() cơ bản để tạo chuỗi thô và ghi trực tiếp bằng FileWriter.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Chuỗi ngẫu nhiên không xử lý lịch trình sẽ sinh ra các ngày lỗi logic như ngày 31/02. \nContextualization: Mã ID nhân viên trong tệp chấm công bắt buộc phải khớp với mã đã sinh ra ở tệp gốc. \nCreative Synthesis: Tôi tự tích hợp thêm thư viện java.time.LocalDate để sinh ngày tháng chính xác. \nDecision: Bọc BufferedWriter xung quanh FileWriter để tối ưu tốc độ ghi đĩa, tránh nghẽn luồng.</t>
+  </si>
+  <si>
+    <t>Tệp dữ liệu mẫu attendance.csv đạt hơn 12,000 dòng.</t>
+  </si>
+  <si>
+    <t>Ánh xạ dữ liệu thô từ file CSV được ngăn cách bằng dấu gạch đứng (|) thành các đối tượng Java để CRUD.</t>
+  </si>
+  <si>
+    <t>Viết hàm tìm kiếm và cập nhật nhân viên dưới file CSV bằng Java sử dụng cơ chế đọc từng dòng và xử lý chuỗi.</t>
+  </si>
+  <si>
+    <t>AI đề xuất đọc file tuần tự, khi tìm thấy ID trùng thì dùng hàm String.replace() trực tiếp trên văn bản của file để sửa đổi dữ liệu.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Lệnh String.replace() trực tiếp dễ làm lệch dòng và hỏng cấu trúc tệp nếu độ dài chuỗi thay đổi. \nContextualization: Hệ thống cần một bộ nhớ đệm để thao tác an toàn trước khi ghi xuống đĩa cứng. \nCreative Synthesis: Tôi tự thiết kế giải pháp nạp dữ liệu vào một tập hợp LinkedHashMap làm bộ nhớ tạm khi khởi chạy. \nDecision: Toàn bộ lệnh CRUD sẽ xử lý trực tiếp trên Map, sau đó mới đồng bộ ghi đè lại file.</t>
+  </si>
+  <si>
+    <t>File nguồn EmployeeRepository.java chứa LinkedHashMap.</t>
+  </si>
+  <si>
+    <t>Viết kịch bản kiểm thử hiệu năng cho tầng lưu trữ, yêu cầu thời gian quét toàn bộ thư mục dữ liệu lớn phải dưới 1 giây.</t>
+  </si>
+  <si>
+    <t>hãy thêm khả năng giới hạn thời gian trong việc đọc tất cả file trong folder data trong tầm 1 giây sử dụng JUnit 5.</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng cấu hình Annotation có sẵn của thư viện: @Timeout(value = 1, unit = TimeUnit.SECONDS) đặt trên đầu hàm test.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Annotation @Timeout sẽ ngắt ngang luồng chạy ngay lập tức khi quá giờ, không đo được số mili-giây cụ thể. \nContextualization: Cần số liệu chi tiết để phân tích lỗi nghẽn cổ chai ở file nào. \nCreative Synthesis: Tôi tự bọc khối mã đọc file bằng hai mốc thời gian System.nanoTime(). \nDecision: Tính hiệu thời gian thực tế tính bằng mili-giây, in ra console và dùng lệnh assertTrue(elapsedMs &lt; 1000.0).</t>
+  </si>
+  <si>
+    <t>Log bảng điều khiển in thông tin: Total processing time: X ms.</t>
+  </si>
+  <si>
+    <t>Triển khai hàm chốt lương runPayroll chạy đơn luồng tuần tự (NO_LOCK), tính tiền thực nhận mà không làm hỏng thiết kế đa hình của nhóm.</t>
+  </si>
+  <si>
+    <t>Viết logic xử lý đơn luồng cho hàm runPayroll kiểm tra trạng thái bảng lương và tính tiền thực nhận cho nhân viên.</t>
+  </si>
+  <si>
+    <t>AI sinh mã code chứa toàn bộ công thức tính toán số tiền lương trực tiếp ngay bên trong vòng lặp điều phối của PayrollController.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhét công thức tính toán vào Controller làm vi phạm tính đóng gói và tính đa hình của OOP. \nContextualization: Nhóm đã chia sẵn lớp con FullTimeEmployee và PartTimeEmployee kế thừa lớp cha. \nCreative Synthesis: Tôi từ chối code AI, bóc tách logic nghiệp vụ tính toán ra khỏi Controller. \nDecision: Chỉ gọi hàm trừu tượng emp.calculateSalary() từ lớp cha, để đối tượng con tự chạy công thức riêng.</t>
+  </si>
+  <si>
+    <t>Mã nguồn hàm runPayroll điều phối chuẩn OOP.</t>
+  </si>
+  <si>
+    <t>Xây dựng chức năng quản lý, nộp và duyệt phép (LeaveController &amp; LeaveView), xử lý nghiêm ngặt các điều kiện biên.</t>
+  </si>
+  <si>
+    <t>Implement LeaveController (submit, approve, reject) và LeaveView (bảng nghỉ phép) và kết nối với LeaveController hãy làm cái này chỉ cái này thôi.</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo cấu trúc điều hướng bằng cách ném ra các mã lỗi dạng số nguyên (Magic Numbers) như: return -1, return -2.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Dùng mã số nguyên làm code cực kỳ tối nghĩa và không tận dụng được Stack Trace của Java. \nContextualization: Ứng dụng nghiệp vụ doanh nghiệp yêu cầu tường minh luồng lỗi. \nCreative Synthesis: Tôi tự tay định nghĩa một lớp ngoại lệ tùy chỉnh riêng tên là InsufficientLeaveBalanceException. \nDecision: Khi nhân viên xin nghỉ quá quyền hạn, Controller sẽ chủ động throw ngoại lệ này ra View.</t>
+  </si>
+  <si>
+    <t>File mã nguồn InsufficientLeaveBalanceException.java.</t>
+  </si>
+  <si>
+    <t>Kết nối tầng View hiển thị bảng lương ASCII với Controller, đảm bảo tuân thủ tuyệt đối nguyên lý bóc tách 3 lớp của MVC.</t>
+  </si>
+  <si>
+    <t>Tạo file ReportView hiển thị bảng lương đẹp mắt dưới dạng ASCII và lấy dữ liệu trực tiếp từ các file lưu trữ để in lên màn hình.</t>
+  </si>
+  <si>
+    <t>AI viết mã code cho lớp ReportView tự gọi và khởi tạo các Repository mới để quét file đĩa và lấy thông tin tên nhân viên.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Tầng View tự ý kết nối thẳng xuống tầng Repository lưu trữ là vi phạm nghiêm trọng kiến trúc MVC. \nContextualization: View chỉ có một nhiệm vụ duy nhất là render định dạng hiển thị bảng biểu. \nCreative Synthesis: Tôi tái cấu trúc hàm renderReport, ép nó chỉ nhận danh sách kết quả List&lt;PayrollEntry&gt; thô. \nDecision: Để lấy tên nhân viên, View phải gọi hàm trung gian từ đối tượng PayrollController để lấy thông tin.</t>
+  </si>
+  <si>
+    <t>File ReportView.java chuẩn cấu trúc MVC.</t>
+  </si>
+  <si>
+    <t>Tích hợp và chạy kiểm thử tự động hóa toàn bộ dự án Maven để kiểm tra đồng bộ logic Tuần 5-6 mà không cần làm Menu nhập liệu.</t>
+  </si>
+  <si>
+    <t>Làm thế nào để tạo menu nhập dữ liệu tương tác từ bàn phím để chạy thử các file View và Controller tuần 5 và tuần 6 vừa viết?</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn tạo một file chạy chính Main.java chứa vòng lặp vô hạn while(true) và dùng thư viện Scanner để nhập tay.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhập dữ liệu thủ công bằng tay rất tốn thời gian và không thể tự động tái sử dụng khi chạy lại. \nContextualization: Dự án được quản lý tự động hoàn toàn bằng công cụ build của Maven. \nCreative Synthesis: Tôi quyết định không làm Menu nhập tay, chuyển dịch sang phương pháp Kiểm thử tự động hóa. \nDecision: Sử dụng file kiểm thử PayrollAndLeaveTest.java để nạp dữ liệu biên giả lập và thực thi tự động.</t>
+  </si>
+  <si>
+    <t>Màn hình Terminal hiển thị kết quả BUILD SUCCESS màu xanh.</t>
   </si>
 </sst>
 </file>
@@ -1569,10 +1635,11 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="18" customWidth="1"/>
-    <col min="2" max="3" width="18" style="18" customWidth="1"/>
-    <col min="4" max="4" width="25" style="18" customWidth="1"/>
-    <col min="5" max="5" width="30" style="18" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="18" style="18" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" style="18" customWidth="1"/>
     <col min="6" max="6" width="35" style="18" customWidth="1"/>
     <col min="7" max="7" width="50" style="18" customWidth="1"/>
     <col min="8" max="8" width="20" style="18" customWidth="1"/>
@@ -1629,132 +1696,212 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
+      <c r="A4" s="7">
+        <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>52</v>
+      <c r="A5" s="7">
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>241</v>
+        <v>39</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>54</v>
+      <c r="A6" s="7">
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
@@ -1967,42 +2114,42 @@
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
